--- a/output/upload/S00026_1772_e연금저축보험_무배당.xlsx
+++ b/output/upload/S00026_1772_e연금저축보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7185,7 +7185,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8837,7 +8837,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -9073,7 +9073,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9722,7 +9722,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -10607,7 +10607,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>177229</t>
+          <t>1772029</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
